--- a/database/event/2720/event_2720_evp_summary.xlsx
+++ b/database/event/2720/event_2720_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.5732</v>
+        <v>7.3277</v>
       </c>
       <c r="C2" t="n">
-        <v>3.3186</v>
+        <v>4.3633</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8301</v>
+        <v>2.4754</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5732</v>
+        <v>7.3277</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4344</v>
+        <v>4.1889</v>
       </c>
       <c r="G2" t="n">
         <v>3.1388</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4344</v>
+        <v>4.2651</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4344</v>
+        <v>4.2651</v>
       </c>
       <c r="J2" t="n">
         <v>3.1388</v>
@@ -529,7 +529,7 @@
         <v>209</v>
       </c>
       <c r="M2" t="n">
-        <v>5.5732</v>
+        <v>7.4039</v>
       </c>
       <c r="N2" t="n">
         <v>284</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.3642</v>
+        <v>5.1193</v>
       </c>
       <c r="C3" t="n">
-        <v>2.5987</v>
+        <v>3.0483</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3417</v>
+        <v>1.5956</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3642</v>
+        <v>5.1193</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5835</v>
+        <v>2.3386</v>
       </c>
       <c r="G3" t="n">
         <v>2.7807</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5835</v>
+        <v>2.3386</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5835</v>
+        <v>2.3386</v>
       </c>
       <c r="J3" t="n">
         <v>2.7807</v>
@@ -575,7 +575,7 @@
         <v>210</v>
       </c>
       <c r="M3" t="n">
-        <v>4.3642</v>
+        <v>5.1193</v>
       </c>
       <c r="N3" t="n">
         <v>341</v>
@@ -584,323 +584,323 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.0139</v>
+        <v>4.5037</v>
       </c>
       <c r="C4" t="n">
-        <v>2.3901</v>
+        <v>2.6818</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2002</v>
+        <v>1.3504</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0139</v>
+        <v>4.5037</v>
       </c>
       <c r="F4" t="n">
-        <v>1.887</v>
+        <v>3.1288</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1269</v>
+        <v>1.3749</v>
       </c>
       <c r="H4" t="n">
-        <v>1.887</v>
+        <v>3.1288</v>
       </c>
       <c r="I4" t="n">
-        <v>1.887</v>
+        <v>3.1288</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1269</v>
+        <v>1.3749</v>
       </c>
       <c r="K4" t="n">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="L4" t="n">
-        <v>209</v>
+        <v>128</v>
       </c>
       <c r="M4" t="n">
-        <v>4.0139</v>
+        <v>4.5037</v>
       </c>
       <c r="N4" t="n">
-        <v>284</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.9167</v>
+        <v>4.4214</v>
       </c>
       <c r="C5" t="n">
-        <v>2.3322</v>
+        <v>2.6327</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1609</v>
+        <v>1.3176</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9167</v>
+        <v>4.4214</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1311</v>
+        <v>4.1997</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7856</v>
+        <v>0.2217</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1311</v>
+        <v>4.2821</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1311</v>
+        <v>4.2821</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7856</v>
+        <v>0.2217</v>
       </c>
       <c r="K5" t="n">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="L5" t="n">
-        <v>209</v>
+        <v>50</v>
       </c>
       <c r="M5" t="n">
-        <v>3.9167</v>
+        <v>4.5038</v>
       </c>
       <c r="N5" t="n">
-        <v>284</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kNgV-</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.862</v>
+        <v>4.331</v>
       </c>
       <c r="C6" t="n">
-        <v>2.2997</v>
+        <v>2.5789</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1388</v>
+        <v>1.2816</v>
       </c>
       <c r="E6" t="n">
-        <v>3.862</v>
+        <v>4.331</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3255</v>
+        <v>3.6151</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5365</v>
+        <v>0.7159</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3255</v>
+        <v>3.6151</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3255</v>
+        <v>3.6151</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5365</v>
+        <v>0.7159</v>
       </c>
       <c r="K6" t="n">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="L6" t="n">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="M6" t="n">
-        <v>3.862</v>
+        <v>4.331</v>
       </c>
       <c r="N6" t="n">
-        <v>341</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>kNgV-</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5551</v>
+        <v>4.2124</v>
       </c>
       <c r="C7" t="n">
-        <v>2.1169</v>
+        <v>2.5083</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0148</v>
+        <v>1.2343</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5551</v>
+        <v>4.2124</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1802</v>
+        <v>1.6759</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3749</v>
+        <v>2.5365</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1802</v>
+        <v>1.6759</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1802</v>
+        <v>1.6759</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3749</v>
+        <v>2.5365</v>
       </c>
       <c r="K7" t="n">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="L7" t="n">
-        <v>128</v>
+        <v>210</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5551</v>
+        <v>4.212400000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>240</v>
+        <v>341</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4749</v>
+        <v>4.1076</v>
       </c>
       <c r="C8" t="n">
-        <v>2.0692</v>
+        <v>2.4459</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9824000000000001</v>
+        <v>1.1926</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4749</v>
+        <v>4.1076</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6979</v>
+        <v>1.322</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7771</v>
+        <v>2.7856</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6979</v>
+        <v>1.322</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6979</v>
+        <v>1.322</v>
       </c>
       <c r="J8" t="n">
-        <v>2.7771</v>
+        <v>2.7856</v>
       </c>
       <c r="K8" t="n">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="L8" t="n">
-        <v>128</v>
+        <v>209</v>
       </c>
       <c r="M8" t="n">
-        <v>3.475</v>
+        <v>4.1076</v>
       </c>
       <c r="N8" t="n">
-        <v>240</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3305</v>
+        <v>4.0844</v>
       </c>
       <c r="C9" t="n">
-        <v>1.9832</v>
+        <v>2.4321</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9241</v>
+        <v>1.1833</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3305</v>
+        <v>4.0844</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8984</v>
+        <v>1.9575</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4321</v>
+        <v>2.1269</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8984</v>
+        <v>1.9575</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8984</v>
+        <v>1.9575</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4321</v>
+        <v>2.1269</v>
       </c>
       <c r="K9" t="n">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="L9" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3305</v>
+        <v>4.0844</v>
       </c>
       <c r="N9" t="n">
-        <v>341</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.1213</v>
+        <v>3.7254</v>
       </c>
       <c r="C10" t="n">
-        <v>1.8586</v>
+        <v>2.2183</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8396</v>
+        <v>1.0403</v>
       </c>
       <c r="E10" t="n">
-        <v>3.1213</v>
+        <v>3.7254</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4054</v>
+        <v>0.9483</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7159</v>
+        <v>2.7771</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4054</v>
+        <v>0.9483</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4054</v>
+        <v>0.9483</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7159</v>
+        <v>2.7771</v>
       </c>
       <c r="K10" t="n">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="L10" t="n">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1213</v>
+        <v>3.7254</v>
       </c>
       <c r="N10" t="n">
-        <v>170</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9918</v>
+        <v>3.6857</v>
       </c>
       <c r="C11" t="n">
-        <v>1.7815</v>
+        <v>2.1947</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7873</v>
+        <v>1.0245</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9918</v>
+        <v>3.6857</v>
       </c>
       <c r="F11" t="n">
-        <v>1.303</v>
+        <v>1.9969</v>
       </c>
       <c r="G11" t="n">
         <v>1.6888</v>
       </c>
       <c r="H11" t="n">
-        <v>1.303</v>
+        <v>1.9969</v>
       </c>
       <c r="I11" t="n">
-        <v>1.303</v>
+        <v>1.9969</v>
       </c>
       <c r="J11" t="n">
         <v>1.6888</v>
@@ -943,7 +943,7 @@
         <v>210</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9918</v>
+        <v>3.6857</v>
       </c>
       <c r="N11" t="n">
         <v>341</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8245</v>
+        <v>3.4214</v>
       </c>
       <c r="C12" t="n">
-        <v>1.6819</v>
+        <v>2.0373</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7197</v>
+        <v>0.9192</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8245</v>
+        <v>3.4214</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6585</v>
+        <v>2.2554</v>
       </c>
       <c r="G12" t="n">
         <v>1.166</v>
       </c>
       <c r="H12" t="n">
-        <v>1.6585</v>
+        <v>2.2554</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6585</v>
+        <v>2.2554</v>
       </c>
       <c r="J12" t="n">
         <v>1.166</v>
@@ -989,7 +989,7 @@
         <v>99</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8245</v>
+        <v>3.4214</v>
       </c>
       <c r="N12" t="n">
         <v>227</v>
@@ -998,47 +998,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6748</v>
+        <v>3.4167</v>
       </c>
       <c r="C13" t="n">
-        <v>1.5927</v>
+        <v>2.0345</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6592</v>
+        <v>0.9173</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6748</v>
+        <v>3.4167</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4531</v>
+        <v>1.9846</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2217</v>
+        <v>1.4321</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4531</v>
+        <v>1.9846</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4531</v>
+        <v>1.9846</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2217</v>
+        <v>1.4321</v>
       </c>
       <c r="K13" t="n">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="L13" t="n">
-        <v>50</v>
+        <v>210</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6748</v>
+        <v>3.4167</v>
       </c>
       <c r="N13" t="n">
-        <v>158</v>
+        <v>341</v>
       </c>
     </row>
     <row r="14">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6557</v>
+        <v>3.0563</v>
       </c>
       <c r="C14" t="n">
-        <v>1.5814</v>
+        <v>1.8199</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6515</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6557</v>
+        <v>3.0563</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6557</v>
+        <v>3.0563</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6557</v>
+        <v>3.0563</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6557</v>
+        <v>3.0563</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6557</v>
+        <v>3.0563</v>
       </c>
       <c r="N14" t="n">
         <v>109</v>
@@ -1090,47 +1090,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5898</v>
+        <v>2.9131</v>
       </c>
       <c r="C15" t="n">
-        <v>1.5421</v>
+        <v>1.7346</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6249</v>
+        <v>0.7167</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5898</v>
+        <v>2.9131</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2237</v>
+        <v>2.8753</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3661</v>
+        <v>0.0378</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2237</v>
+        <v>2.8753</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2237</v>
+        <v>2.8753</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3661</v>
+        <v>0.0378</v>
       </c>
       <c r="K15" t="n">
-        <v>128</v>
+        <v>81</v>
       </c>
       <c r="L15" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="M15" t="n">
-        <v>2.5898</v>
+        <v>2.9131</v>
       </c>
       <c r="N15" t="n">
-        <v>227</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1768</v>
+        <v>2.7722</v>
       </c>
       <c r="C16" t="n">
-        <v>1.2962</v>
+        <v>1.6507</v>
       </c>
       <c r="D16" t="n">
-        <v>0.458</v>
+        <v>0.6605</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1768</v>
+        <v>2.7722</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3481</v>
+        <v>2.9435</v>
       </c>
       <c r="G16" t="n">
         <v>-0.1713</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3481</v>
+        <v>2.9435</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3481</v>
+        <v>2.9435</v>
       </c>
       <c r="J16" t="n">
         <v>-0.1713</v>
@@ -1173,7 +1173,7 @@
         <v>99</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1768</v>
+        <v>2.7722</v>
       </c>
       <c r="N16" t="n">
         <v>227</v>
@@ -1182,829 +1182,829 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1207</v>
+        <v>2.6873</v>
       </c>
       <c r="C17" t="n">
-        <v>1.2628</v>
+        <v>1.6002</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4354</v>
+        <v>0.6267</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1207</v>
+        <v>2.6873</v>
       </c>
       <c r="F17" t="n">
-        <v>1.913</v>
+        <v>1.3064</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2077</v>
+        <v>1.3809</v>
       </c>
       <c r="H17" t="n">
-        <v>1.913</v>
+        <v>1.3064</v>
       </c>
       <c r="I17" t="n">
-        <v>1.913</v>
+        <v>1.3064</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2077</v>
+        <v>1.3809</v>
       </c>
       <c r="K17" t="n">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="L17" t="n">
-        <v>50</v>
+        <v>210</v>
       </c>
       <c r="M17" t="n">
-        <v>2.1207</v>
+        <v>2.6873</v>
       </c>
       <c r="N17" t="n">
-        <v>158</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9688</v>
+        <v>2.6794</v>
       </c>
       <c r="C18" t="n">
-        <v>1.1723</v>
+        <v>1.5955</v>
       </c>
       <c r="D18" t="n">
-        <v>0.374</v>
+        <v>0.6236</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9688</v>
+        <v>2.6794</v>
       </c>
       <c r="F18" t="n">
-        <v>1.931</v>
+        <v>1.3133</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0378</v>
+        <v>1.3661</v>
       </c>
       <c r="H18" t="n">
-        <v>1.931</v>
+        <v>1.3133</v>
       </c>
       <c r="I18" t="n">
-        <v>1.931</v>
+        <v>1.3133</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0378</v>
+        <v>1.3661</v>
       </c>
       <c r="K18" t="n">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="L18" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="M18" t="n">
-        <v>1.9688</v>
+        <v>2.6794</v>
       </c>
       <c r="N18" t="n">
-        <v>170</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.8895</v>
+        <v>2.6434</v>
       </c>
       <c r="C19" t="n">
-        <v>1.1251</v>
+        <v>1.574</v>
       </c>
       <c r="D19" t="n">
-        <v>0.342</v>
+        <v>0.6092</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8895</v>
+        <v>2.6434</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8895</v>
+        <v>3.2314</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.588</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8895</v>
+        <v>3.2314</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8895</v>
+        <v>3.2314</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.588</v>
       </c>
       <c r="K19" t="n">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M19" t="n">
-        <v>1.8895</v>
+        <v>2.6434</v>
       </c>
       <c r="N19" t="n">
-        <v>130</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.7751</v>
+        <v>2.3004</v>
       </c>
       <c r="C20" t="n">
-        <v>1.057</v>
+        <v>1.3698</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2957</v>
+        <v>0.4726</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7751</v>
+        <v>2.3004</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7446</v>
+        <v>2.0927</v>
       </c>
       <c r="G20" t="n">
-        <v>1.0305</v>
+        <v>0.2077</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7446</v>
+        <v>2.0927</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7446</v>
+        <v>2.0927</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0305</v>
+        <v>0.2077</v>
       </c>
       <c r="K20" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="L20" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="M20" t="n">
-        <v>1.7751</v>
+        <v>2.3004</v>
       </c>
       <c r="N20" t="n">
-        <v>227</v>
+        <v>158</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.7695</v>
+        <v>2.139</v>
       </c>
       <c r="C21" t="n">
-        <v>1.0537</v>
+        <v>1.2737</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2935</v>
+        <v>0.4083</v>
       </c>
       <c r="E21" t="n">
-        <v>1.7695</v>
+        <v>2.139</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3886</v>
+        <v>1.9977</v>
       </c>
       <c r="G21" t="n">
-        <v>1.3809</v>
+        <v>0.1413</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3886</v>
+        <v>1.9977</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3886</v>
+        <v>1.9977</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3809</v>
+        <v>0.1413</v>
       </c>
       <c r="K21" t="n">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="L21" t="n">
-        <v>210</v>
+        <v>51</v>
       </c>
       <c r="M21" t="n">
-        <v>1.7695</v>
+        <v>2.139</v>
       </c>
       <c r="N21" t="n">
-        <v>341</v>
+        <v>168</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.7689</v>
+        <v>1.9948</v>
       </c>
       <c r="C22" t="n">
-        <v>1.0533</v>
+        <v>1.1878</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2932</v>
+        <v>0.3508</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7689</v>
+        <v>1.9948</v>
       </c>
       <c r="F22" t="n">
-        <v>2.3569</v>
+        <v>1.9948</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.588</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.3569</v>
+        <v>1.9948</v>
       </c>
       <c r="I22" t="n">
-        <v>2.3569</v>
+        <v>1.9948</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.588</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="L22" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.7689</v>
+        <v>1.9948</v>
       </c>
       <c r="N22" t="n">
-        <v>168</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.5925</v>
+        <v>1.9482</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9483</v>
+        <v>1.1601</v>
       </c>
       <c r="D23" t="n">
-        <v>0.222</v>
+        <v>0.3323</v>
       </c>
       <c r="E23" t="n">
-        <v>1.5925</v>
+        <v>1.9482</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5925</v>
+        <v>0.9177</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1.0305</v>
       </c>
       <c r="H23" t="n">
-        <v>1.5925</v>
+        <v>0.9177</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5925</v>
+        <v>0.9177</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1.0305</v>
       </c>
       <c r="K23" t="n">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="M23" t="n">
-        <v>1.5925</v>
+        <v>1.9482</v>
       </c>
       <c r="N23" t="n">
-        <v>113</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>wayLander</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.4742</v>
+        <v>1.9404</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8778</v>
+        <v>1.1554</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1742</v>
+        <v>0.3291</v>
       </c>
       <c r="E24" t="n">
-        <v>1.4742</v>
+        <v>1.9404</v>
       </c>
       <c r="F24" t="n">
-        <v>1.4742</v>
+        <v>1.9404</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.4742</v>
+        <v>1.9404</v>
       </c>
       <c r="I24" t="n">
-        <v>1.4742</v>
+        <v>1.9404</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.4742</v>
+        <v>1.9404</v>
       </c>
       <c r="N24" t="n">
-        <v>144</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.4217</v>
+        <v>1.9285</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8466</v>
+        <v>1.1483</v>
       </c>
       <c r="D25" t="n">
-        <v>0.153</v>
+        <v>0.3244</v>
       </c>
       <c r="E25" t="n">
-        <v>1.4217</v>
+        <v>1.9285</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8582</v>
+        <v>1.9285</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5635</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8582</v>
+        <v>1.9285</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8582</v>
+        <v>1.9285</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5635</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="L25" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.4217</v>
+        <v>1.9285</v>
       </c>
       <c r="N25" t="n">
-        <v>197</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.3561</v>
+        <v>1.8164</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8075</v>
+        <v>1.0816</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1265</v>
+        <v>0.2797</v>
       </c>
       <c r="E26" t="n">
-        <v>1.3561</v>
+        <v>1.8164</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5375</v>
+        <v>1.6229</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8186</v>
+        <v>0.1935</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5375</v>
+        <v>1.6229</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5375</v>
+        <v>1.6229</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8186</v>
+        <v>0.1935</v>
       </c>
       <c r="K26" t="n">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="L26" t="n">
-        <v>209</v>
+        <v>128</v>
       </c>
       <c r="M26" t="n">
-        <v>1.3561</v>
+        <v>1.8164</v>
       </c>
       <c r="N26" t="n">
-        <v>284</v>
+        <v>240</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.2353</v>
+        <v>1.5574</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7356</v>
+        <v>0.9274</v>
       </c>
       <c r="D27" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.1766</v>
       </c>
       <c r="E27" t="n">
-        <v>1.2353</v>
+        <v>1.5574</v>
       </c>
       <c r="F27" t="n">
-        <v>1.094</v>
+        <v>0.9939</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1413</v>
+        <v>0.5635</v>
       </c>
       <c r="H27" t="n">
-        <v>1.094</v>
+        <v>0.9939</v>
       </c>
       <c r="I27" t="n">
-        <v>1.094</v>
+        <v>0.9939</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1413</v>
+        <v>0.5635</v>
       </c>
       <c r="K27" t="n">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="L27" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="M27" t="n">
-        <v>1.2353</v>
+        <v>1.5574</v>
       </c>
       <c r="N27" t="n">
-        <v>168</v>
+        <v>197</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>wayLander</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.1695</v>
+        <v>1.5402</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6964</v>
+        <v>0.9171</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0511</v>
+        <v>0.1697</v>
       </c>
       <c r="E28" t="n">
-        <v>1.1695</v>
+        <v>1.5402</v>
       </c>
       <c r="F28" t="n">
-        <v>1.1695</v>
+        <v>1.5402</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.1695</v>
+        <v>1.5402</v>
       </c>
       <c r="I28" t="n">
-        <v>1.1695</v>
+        <v>1.5402</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1695</v>
+        <v>1.5402</v>
       </c>
       <c r="N28" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.1209</v>
+        <v>1.3866</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6674</v>
+        <v>0.8257</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0315</v>
+        <v>0.1085</v>
       </c>
       <c r="E29" t="n">
-        <v>1.1209</v>
+        <v>1.3866</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9274</v>
+        <v>2.5264</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1935</v>
+        <v>-1.1398</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9274</v>
+        <v>2.5264</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9274</v>
+        <v>2.5264</v>
       </c>
       <c r="J29" t="n">
-        <v>0.1935</v>
+        <v>-1.1398</v>
       </c>
       <c r="K29" t="n">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="L29" t="n">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="M29" t="n">
-        <v>1.1209</v>
+        <v>1.3866</v>
       </c>
       <c r="N29" t="n">
-        <v>240</v>
+        <v>227</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.0473</v>
+        <v>1.3561</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6236</v>
+        <v>0.8075</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0017</v>
+        <v>0.0964</v>
       </c>
       <c r="E30" t="n">
-        <v>1.0473</v>
+        <v>1.3561</v>
       </c>
       <c r="F30" t="n">
-        <v>1.0473</v>
+        <v>0.5375</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.8186</v>
       </c>
       <c r="H30" t="n">
-        <v>1.0473</v>
+        <v>0.5375</v>
       </c>
       <c r="I30" t="n">
-        <v>1.0473</v>
+        <v>0.5375</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.8186</v>
       </c>
       <c r="K30" t="n">
-        <v>144</v>
+        <v>75</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="M30" t="n">
-        <v>1.0473</v>
+        <v>1.3561</v>
       </c>
       <c r="N30" t="n">
-        <v>144</v>
+        <v>284</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9714</v>
+        <v>1.2309</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5784</v>
+        <v>0.7329</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0289</v>
+        <v>0.0465</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9714</v>
+        <v>1.2309</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9448</v>
+        <v>1.2309</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0266</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9448</v>
+        <v>1.2309</v>
       </c>
       <c r="I31" t="n">
-        <v>0.9448</v>
+        <v>1.2309</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0266</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="L31" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.9713999999999999</v>
+        <v>1.2309</v>
       </c>
       <c r="N31" t="n">
-        <v>197</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9555</v>
+        <v>1.1609</v>
       </c>
       <c r="C32" t="n">
-        <v>0.569</v>
+        <v>0.6913</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0354</v>
+        <v>0.0186</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9555</v>
+        <v>1.1609</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9555</v>
+        <v>1.1343</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.0266</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9555</v>
+        <v>1.1343</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9555</v>
+        <v>1.1343</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>0.0266</v>
       </c>
       <c r="K32" t="n">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="M32" t="n">
-        <v>0.9555</v>
+        <v>1.1609</v>
       </c>
       <c r="N32" t="n">
-        <v>84</v>
+        <v>197</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>denis</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9359</v>
+        <v>1.0363</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5573</v>
+        <v>0.6171</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0433</v>
+        <v>-0.031</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9359</v>
+        <v>1.0363</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9359</v>
+        <v>1.3118</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.2755</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9359</v>
+        <v>1.3118</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9359</v>
+        <v>1.3118</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.2755</v>
       </c>
       <c r="K33" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="M33" t="n">
-        <v>0.9359</v>
+        <v>1.0363</v>
       </c>
       <c r="N33" t="n">
-        <v>121</v>
+        <v>240</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>zehN</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9302</v>
+        <v>0.9597</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.5715</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0456</v>
+        <v>-0.0616</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9302</v>
+        <v>0.9597</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9302</v>
+        <v>0.9597</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9302</v>
+        <v>0.9597</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9302</v>
+        <v>0.9597</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.9302</v>
+        <v>0.9597</v>
       </c>
       <c r="N34" t="n">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.9366</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5459000000000001</v>
+        <v>0.5577</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.051</v>
+        <v>-0.0708</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.9366</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.9366</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.9366</v>
       </c>
       <c r="I35" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.9366</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.9366</v>
       </c>
       <c r="N35" t="n">
         <v>144</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>denis</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8675</v>
+        <v>0.9359</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5165999999999999</v>
+        <v>0.5573</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0709</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8675</v>
+        <v>0.9359</v>
       </c>
       <c r="F36" t="n">
-        <v>1.143</v>
+        <v>0.9359</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.2755</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.143</v>
+        <v>0.9359</v>
       </c>
       <c r="I36" t="n">
-        <v>1.143</v>
+        <v>0.9359</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.2755</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L36" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8674999999999999</v>
+        <v>0.9359</v>
       </c>
       <c r="N36" t="n">
-        <v>240</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>zehN</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6728</v>
+        <v>0.9302</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4006</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1496</v>
+        <v>-0.0733</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6728</v>
+        <v>0.9302</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6728</v>
+        <v>0.9302</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6728</v>
+        <v>0.9302</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6728</v>
+        <v>0.9302</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.6728</v>
+        <v>0.9302</v>
       </c>
       <c r="N37" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6465</v>
+        <v>0.9209000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>0.385</v>
+        <v>0.5484</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1602</v>
+        <v>-0.077</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6465</v>
+        <v>0.9209000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6465</v>
+        <v>0.9209000000000001</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6465</v>
+        <v>0.9209000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6465</v>
+        <v>0.9209000000000001</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.6465</v>
+        <v>0.9209000000000001</v>
       </c>
       <c r="N38" t="n">
         <v>109</v>
@@ -2194,277 +2194,277 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6372</v>
+        <v>0.788</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3794</v>
+        <v>0.4692</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1639</v>
+        <v>-0.13</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6372</v>
+        <v>0.788</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6372</v>
+        <v>1.4478</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.6598000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6372</v>
+        <v>1.4478</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6372</v>
+        <v>1.4478</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.6598000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M39" t="n">
-        <v>0.6372</v>
+        <v>0.7879999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>84</v>
+        <v>168</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5659</v>
+        <v>0.7257</v>
       </c>
       <c r="C40" t="n">
-        <v>0.337</v>
+        <v>0.4321</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1928</v>
+        <v>-0.1548</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5659</v>
+        <v>0.7257</v>
       </c>
       <c r="F40" t="n">
-        <v>1.2257</v>
+        <v>1.1026</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.6598000000000001</v>
+        <v>-0.3769</v>
       </c>
       <c r="H40" t="n">
-        <v>1.2257</v>
+        <v>1.1026</v>
       </c>
       <c r="I40" t="n">
-        <v>1.2257</v>
+        <v>1.1026</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.6598000000000001</v>
+        <v>-0.3769</v>
       </c>
       <c r="K40" t="n">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="L40" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="M40" t="n">
-        <v>0.5659</v>
+        <v>0.7257</v>
       </c>
       <c r="N40" t="n">
-        <v>168</v>
+        <v>197</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.499</v>
+        <v>0.695</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2971</v>
+        <v>0.4138</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2198</v>
+        <v>-0.167</v>
       </c>
       <c r="E41" t="n">
-        <v>0.499</v>
+        <v>0.695</v>
       </c>
       <c r="F41" t="n">
-        <v>1.6388</v>
+        <v>0.695</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.1398</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.6388</v>
+        <v>0.695</v>
       </c>
       <c r="I41" t="n">
-        <v>1.6388</v>
+        <v>0.695</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.1398</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="L41" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4990000000000001</v>
+        <v>0.695</v>
       </c>
       <c r="N41" t="n">
-        <v>227</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>markeloff</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4756</v>
+        <v>0.6728</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2832</v>
+        <v>0.4006</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2292</v>
+        <v>-0.1759</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4756</v>
+        <v>0.6728</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4756</v>
+        <v>0.6728</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4756</v>
+        <v>0.6728</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4756</v>
+        <v>0.6728</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.4756</v>
+        <v>0.6728</v>
       </c>
       <c r="N42" t="n">
-        <v>130</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>markeloff</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4543</v>
+        <v>0.5527</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2705</v>
+        <v>0.3291</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2378</v>
+        <v>-0.2237</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4543</v>
+        <v>0.5527</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9839</v>
+        <v>0.5527</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.5296</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9839</v>
+        <v>0.5527</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9839</v>
+        <v>0.5527</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.5296</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="L43" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.4543</v>
+        <v>0.5527</v>
       </c>
       <c r="N43" t="n">
-        <v>158</v>
+        <v>130</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4339</v>
+        <v>0.4798</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2584</v>
+        <v>0.2857</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2461</v>
+        <v>-0.2528</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4339</v>
+        <v>0.4798</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8108</v>
+        <v>1.0094</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.3769</v>
+        <v>-0.5296</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8108</v>
+        <v>1.0094</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8108</v>
+        <v>1.0094</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.3769</v>
+        <v>-0.5296</v>
       </c>
       <c r="K44" t="n">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="L44" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M44" t="n">
-        <v>0.4339</v>
+        <v>0.4798000000000001</v>
       </c>
       <c r="N44" t="n">
-        <v>197</v>
+        <v>158</v>
       </c>
     </row>
     <row r="45">
@@ -2480,7 +2480,7 @@
         <v>0.2532</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2496</v>
+        <v>-0.2745</v>
       </c>
       <c r="E45" t="n">
         <v>0.4253</v>
@@ -2526,7 +2526,7 @@
         <v>0.1775</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3009</v>
+        <v>-0.3251</v>
       </c>
       <c r="E46" t="n">
         <v>0.2981</v>
@@ -2562,139 +2562,139 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.2338</v>
+        <v>0.2457</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1392</v>
+        <v>0.1463</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3269</v>
+        <v>-0.346</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2338</v>
+        <v>0.2457</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2338</v>
+        <v>0.2457</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2338</v>
+        <v>0.2457</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2338</v>
+        <v>0.2457</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.2338</v>
+        <v>0.2457</v>
       </c>
       <c r="N47" t="n">
-        <v>70</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.1969</v>
+        <v>0.2338</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1172</v>
+        <v>0.1392</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3418</v>
+        <v>-0.3508</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1969</v>
+        <v>0.2338</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1969</v>
+        <v>0.2338</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1969</v>
+        <v>0.2338</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1969</v>
+        <v>0.2338</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1969</v>
+        <v>0.2338</v>
       </c>
       <c r="N48" t="n">
-        <v>113</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>HS</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.1902</v>
+        <v>0.1969</v>
       </c>
       <c r="C49" t="n">
-        <v>0.1133</v>
+        <v>0.1172</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3445</v>
+        <v>-0.3655</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1902</v>
+        <v>0.1969</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1902</v>
+        <v>0.1969</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1902</v>
+        <v>0.1969</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1902</v>
+        <v>0.1969</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.1902</v>
+        <v>0.1969</v>
       </c>
       <c r="N49" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50">
@@ -2710,7 +2710,7 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3787</v>
+        <v>-0.4019</v>
       </c>
       <c r="E50" t="n">
         <v>0.1055</v>
@@ -2746,47 +2746,47 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>keev</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.0383</v>
+        <v>0.0998</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0228</v>
+        <v>0.0594</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4059</v>
+        <v>-0.4042</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0383</v>
+        <v>0.0998</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0383</v>
+        <v>0.611</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>-0.5112</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0383</v>
+        <v>0.611</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0383</v>
+        <v>0.611</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>-0.5112</v>
       </c>
       <c r="K51" t="n">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="M51" t="n">
-        <v>0.0383</v>
+        <v>0.0998</v>
       </c>
       <c r="N51" t="n">
-        <v>136</v>
+        <v>170</v>
       </c>
     </row>
     <row r="52">
@@ -2796,28 +2796,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.0243</v>
+        <v>0.048</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0145</v>
+        <v>0.0286</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4115</v>
+        <v>-0.4248</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0243</v>
+        <v>0.048</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0243</v>
+        <v>0.048</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0243</v>
+        <v>0.048</v>
       </c>
       <c r="I52" t="n">
-        <v>0.0243</v>
+        <v>0.048</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.0243</v>
+        <v>0.048</v>
       </c>
       <c r="N52" t="n">
         <v>121</v>
@@ -2838,277 +2838,277 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>keev</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.0335</v>
+        <v>0.0439</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0199</v>
+        <v>0.0261</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4349</v>
+        <v>-0.4264</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.0335</v>
+        <v>0.0439</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4777</v>
+        <v>0.0439</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.5112</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.4777</v>
+        <v>0.0439</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4777</v>
+        <v>0.0439</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.5112</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>81</v>
+        <v>144</v>
       </c>
       <c r="L53" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.03349999999999997</v>
+        <v>0.0439</v>
       </c>
       <c r="N53" t="n">
-        <v>170</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kRYSTAL</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.0398</v>
+        <v>0.0383</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0237</v>
+        <v>0.0228</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4374</v>
+        <v>-0.4287</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.0398</v>
+        <v>0.0383</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.0398</v>
+        <v>0.0383</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.0398</v>
+        <v>0.0383</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.0398</v>
+        <v>0.0383</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.0398</v>
+        <v>0.0383</v>
       </c>
       <c r="N54" t="n">
-        <v>113</v>
+        <v>136</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>WorldEdit</t>
+          <t>kRYSTAL</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.1562</v>
+        <v>-0.0398</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.093</v>
+        <v>-0.0237</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4845</v>
+        <v>-0.4598</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.1562</v>
+        <v>-0.0398</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.1562</v>
+        <v>-0.0398</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.1562</v>
+        <v>-0.0398</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1562</v>
+        <v>-0.0398</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.1562</v>
+        <v>-0.0398</v>
       </c>
       <c r="N55" t="n">
-        <v>130</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>WorldEdit</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.1994</v>
+        <v>-0.1562</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1187</v>
+        <v>-0.093</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5019</v>
+        <v>-0.5061</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.1994</v>
+        <v>-0.1562</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.1994</v>
+        <v>-0.1562</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.1994</v>
+        <v>-0.1562</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1994</v>
+        <v>-0.1562</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.1994</v>
+        <v>-0.1562</v>
       </c>
       <c r="N56" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.2161</v>
+        <v>-0.1979</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.1287</v>
+        <v>-0.1178</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5087</v>
+        <v>-0.5228</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.2161</v>
+        <v>-0.1979</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.2161</v>
+        <v>-0.1979</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.2161</v>
+        <v>-0.1979</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.2161</v>
+        <v>-0.1979</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.2161</v>
+        <v>-0.1979</v>
       </c>
       <c r="N57" t="n">
-        <v>84</v>
+        <v>136</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.3445</v>
+        <v>-0.2161</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2051</v>
+        <v>-0.1287</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5605</v>
+        <v>-0.53</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.3445</v>
+        <v>-0.2161</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.3445</v>
+        <v>-0.2161</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.3445</v>
+        <v>-0.2161</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.3445</v>
+        <v>-0.2161</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>144</v>
+        <v>84</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.3445</v>
+        <v>-0.2161</v>
       </c>
       <c r="N58" t="n">
-        <v>144</v>
+        <v>84</v>
       </c>
     </row>
     <row r="59">
@@ -3124,7 +3124,7 @@
         <v>-0.2474</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5891999999999999</v>
+        <v>-0.6094000000000001</v>
       </c>
       <c r="E59" t="n">
         <v>-0.4154</v>
@@ -3170,7 +3170,7 @@
         <v>-0.2631</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5999</v>
+        <v>-0.62</v>
       </c>
       <c r="E60" t="n">
         <v>-0.4419</v>
@@ -3216,7 +3216,7 @@
         <v>-0.3136</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6341</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="E61" t="n">
         <v>-0.5266999999999999</v>
@@ -3262,7 +3262,7 @@
         <v>-0.314</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6344</v>
+        <v>-0.654</v>
       </c>
       <c r="E62" t="n">
         <v>-0.5274</v>
@@ -3298,400 +3298,400 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.6545</v>
+        <v>-0.6454</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.3897</v>
+        <v>-0.3843</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6858</v>
+        <v>-0.701</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.6545</v>
+        <v>-0.6454</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.6545</v>
+        <v>-0.0025</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>-0.6429</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.6545</v>
+        <v>-0.0025</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.6545</v>
+        <v>-0.0025</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>-0.6429</v>
       </c>
       <c r="K63" t="n">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.6545</v>
+        <v>-0.6454</v>
       </c>
       <c r="N63" t="n">
-        <v>121</v>
+        <v>158</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>keshandr</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.8329</v>
+        <v>-0.6464</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.496</v>
+        <v>-0.3849</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7578</v>
+        <v>-0.7014</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.8329</v>
+        <v>-0.6464</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.8329</v>
+        <v>-0.6464</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.8329</v>
+        <v>-0.6464</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.8329</v>
+        <v>-0.6464</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.8329</v>
+        <v>-0.6464</v>
       </c>
       <c r="N64" t="n">
-        <v>70</v>
+        <v>109</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>innocent</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.8819</v>
+        <v>-0.6545</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.5251</v>
+        <v>-0.3897</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7776</v>
+        <v>-0.7047</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.8819</v>
+        <v>-0.6545</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.8819</v>
+        <v>-0.6545</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.8819</v>
+        <v>-0.6545</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.8819</v>
+        <v>-0.6545</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.8819</v>
+        <v>-0.6545</v>
       </c>
       <c r="N65" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>innocent</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.9208</v>
+        <v>-0.8138</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.5483</v>
+        <v>-0.4846</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7933</v>
+        <v>-0.7681</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.9208</v>
+        <v>-0.8138</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.9208</v>
+        <v>-0.8138</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.9208</v>
+        <v>-0.8138</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.9208</v>
+        <v>-0.8138</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.9208</v>
+        <v>-0.8138</v>
       </c>
       <c r="N66" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>keshandr</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.9842</v>
+        <v>-0.8329</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.586</v>
+        <v>-0.496</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.819</v>
+        <v>-0.7756999999999999</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.9842</v>
+        <v>-0.8329</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.2601</v>
+        <v>-0.8329</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.7241</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.2601</v>
+        <v>-0.8329</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.2601</v>
+        <v>-0.8329</v>
       </c>
       <c r="J67" t="n">
-        <v>-0.7241</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>139</v>
+        <v>70</v>
       </c>
       <c r="L67" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.9842</v>
+        <v>-0.8329</v>
       </c>
       <c r="N67" t="n">
-        <v>197</v>
+        <v>70</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>LEGIJA</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.0081</v>
+        <v>-0.9842</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.6002999999999999</v>
+        <v>-0.586</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8286</v>
+        <v>-0.836</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.0081</v>
+        <v>-0.9842</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.893</v>
+        <v>-0.2601</v>
       </c>
       <c r="G68" t="n">
-        <v>0.8849</v>
+        <v>-0.7241</v>
       </c>
       <c r="H68" t="n">
-        <v>-1.893</v>
+        <v>-0.2601</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.893</v>
+        <v>-0.2601</v>
       </c>
       <c r="J68" t="n">
-        <v>0.8849</v>
+        <v>-0.7241</v>
       </c>
       <c r="K68" t="n">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="L68" t="n">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="M68" t="n">
-        <v>-1.0081</v>
+        <v>-0.9842</v>
       </c>
       <c r="N68" t="n">
-        <v>170</v>
+        <v>197</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>LEGIJA</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.1767</v>
+        <v>-1.0081</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.7007</v>
+        <v>-0.6002999999999999</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8967000000000001</v>
+        <v>-0.8455</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.1767</v>
+        <v>-1.0081</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.1767</v>
+        <v>-1.893</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>0.8849</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.1767</v>
+        <v>-1.893</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.1767</v>
+        <v>-1.893</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>0.8849</v>
       </c>
       <c r="K69" t="n">
-        <v>136</v>
+        <v>81</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="M69" t="n">
-        <v>-1.1767</v>
+        <v>-1.0081</v>
       </c>
       <c r="N69" t="n">
-        <v>136</v>
+        <v>170</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>jR</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.3768</v>
+        <v>-1.1767</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.8198</v>
+        <v>-0.7007</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9776</v>
+        <v>-0.9127</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.3768</v>
+        <v>-1.1767</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.3768</v>
+        <v>-1.1767</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.3768</v>
+        <v>-1.1767</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.3768</v>
+        <v>-1.1767</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>70</v>
+        <v>136</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-1.3768</v>
+        <v>-1.1767</v>
       </c>
       <c r="N70" t="n">
-        <v>70</v>
+        <v>136</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>jR</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.3901</v>
+        <v>-1.3768</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.8277</v>
+        <v>-0.8198</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9829</v>
+        <v>-0.9923999999999999</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.3901</v>
+        <v>-1.3768</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.3901</v>
+        <v>-1.3768</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.3901</v>
+        <v>-1.3768</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.3901</v>
+        <v>-1.3768</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-1.3901</v>
+        <v>-1.3768</v>
       </c>
       <c r="N71" t="n">
         <v>70</v>
@@ -3712,93 +3712,93 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>gob b</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.4279</v>
+        <v>-1.3901</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.8502999999999999</v>
+        <v>-0.8277</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9982</v>
+        <v>-0.9977</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.4279</v>
+        <v>-1.3901</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.4573</v>
+        <v>-1.3901</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.9706</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.4573</v>
+        <v>-1.3901</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.4573</v>
+        <v>-1.3901</v>
       </c>
       <c r="J72" t="n">
-        <v>-0.9706</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="L72" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-1.4279</v>
+        <v>-1.3901</v>
       </c>
       <c r="N72" t="n">
-        <v>170</v>
+        <v>70</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>gob b</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.5761</v>
+        <v>-1.4279</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.9385</v>
+        <v>-0.8502999999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0581</v>
+        <v>-1.0128</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.5761</v>
+        <v>-1.4279</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.9332</v>
+        <v>-0.4573</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.6429</v>
+        <v>-0.9706</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.9332</v>
+        <v>-0.4573</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.9332</v>
+        <v>-0.4573</v>
       </c>
       <c r="J73" t="n">
-        <v>-0.6429</v>
+        <v>-0.9706</v>
       </c>
       <c r="K73" t="n">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="L73" t="n">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.5761</v>
+        <v>-1.4279</v>
       </c>
       <c r="N73" t="n">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="74">
@@ -3814,7 +3814,7 @@
         <v>-0.953</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0679</v>
+        <v>-1.0815</v>
       </c>
       <c r="E74" t="n">
         <v>-1.6005</v>
@@ -3860,7 +3860,7 @@
         <v>-1.0018</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.101</v>
+        <v>-1.1142</v>
       </c>
       <c r="E75" t="n">
         <v>-1.6824</v>
@@ -3906,7 +3906,7 @@
         <v>-1.0911</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1616</v>
+        <v>-1.1739</v>
       </c>
       <c r="E76" t="n">
         <v>-1.8324</v>
@@ -3952,7 +3952,7 @@
         <v>-1.1382</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1936</v>
+        <v>-1.2055</v>
       </c>
       <c r="E77" t="n">
         <v>-1.9115</v>
@@ -3998,7 +3998,7 @@
         <v>-1.1514</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2025</v>
+        <v>-1.2143</v>
       </c>
       <c r="E78" t="n">
         <v>-1.9336</v>
@@ -4044,7 +4044,7 @@
         <v>-1.183</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.2239</v>
+        <v>-1.2354</v>
       </c>
       <c r="E79" t="n">
         <v>-1.9867</v>
@@ -4090,7 +4090,7 @@
         <v>-1.6716</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.5554</v>
+        <v>-1.5623</v>
       </c>
       <c r="E80" t="n">
         <v>-2.8072</v>
@@ -4136,7 +4136,7 @@
         <v>-2.01</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.785</v>
+        <v>-1.7887</v>
       </c>
       <c r="E81" t="n">
         <v>-3.3755</v>
